--- a/Data_Analysis/Sensitivity analysis/Hybrid/sweep_results_hybrid_G1_task031.xlsx
+++ b/Data_Analysis/Sensitivity analysis/Hybrid/sweep_results_hybrid_G1_task031.xlsx
@@ -100,13 +100,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N2"/>
+  <dimension ref="A1:N11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="7.85546875" customWidth="true"/>
     <col min="2" max="2" width="14.85546875" customWidth="true"/>
     <col min="3" max="3" width="13.28515625" customWidth="true"/>
-    <col min="4" max="4" width="10" customWidth="true"/>
+    <col min="4" max="4" width="11.7109375" customWidth="true"/>
     <col min="5" max="5" width="9.5703125" customWidth="true"/>
     <col min="6" max="6" width="16.140625" customWidth="true"/>
     <col min="7" max="7" width="20.85546875" customWidth="true"/>
@@ -207,6 +207,402 @@
         <v>5.2729357775983692</v>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" s="0">
+        <v>103</v>
+      </c>
+      <c r="B3" s="0">
+        <v>302</v>
+      </c>
+      <c r="C3" s="0">
+        <v>103</v>
+      </c>
+      <c r="D3" s="0">
+        <v>94.173169514385364</v>
+      </c>
+      <c r="E3" s="0">
+        <v>467.88</v>
+      </c>
+      <c r="F3" s="0">
+        <v>157.41555991608288</v>
+      </c>
+      <c r="G3" s="0">
+        <v>3591.2657177546312</v>
+      </c>
+      <c r="H3" s="0">
+        <v>-988.96944752242348</v>
+      </c>
+      <c r="I3" s="0">
+        <v>5.7999999999999998</v>
+      </c>
+      <c r="J3" s="0">
+        <v>14.865</v>
+      </c>
+      <c r="K3" s="0">
+        <v>2.46</v>
+      </c>
+      <c r="L3" s="0">
+        <v>3.5200000000000005</v>
+      </c>
+      <c r="M3" s="0">
+        <v>300.05811227880264</v>
+      </c>
+      <c r="N3" s="0">
+        <v>5.2729357775983692</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="0">
+        <v>103</v>
+      </c>
+      <c r="B4" s="0">
+        <v>303</v>
+      </c>
+      <c r="C4" s="0">
+        <v>103</v>
+      </c>
+      <c r="D4" s="0">
+        <v>94.173169514385364</v>
+      </c>
+      <c r="E4" s="0">
+        <v>467.88</v>
+      </c>
+      <c r="F4" s="0">
+        <v>157.41555991608288</v>
+      </c>
+      <c r="G4" s="0">
+        <v>3591.2657177546312</v>
+      </c>
+      <c r="H4" s="0">
+        <v>-988.96944752242348</v>
+      </c>
+      <c r="I4" s="0">
+        <v>5.7999999999999998</v>
+      </c>
+      <c r="J4" s="0">
+        <v>14.865</v>
+      </c>
+      <c r="K4" s="0">
+        <v>2.46</v>
+      </c>
+      <c r="L4" s="0">
+        <v>3.5200000000000005</v>
+      </c>
+      <c r="M4" s="0">
+        <v>300.05811227880264</v>
+      </c>
+      <c r="N4" s="0">
+        <v>5.2729357775983692</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="0">
+        <v>103</v>
+      </c>
+      <c r="B5" s="0">
+        <v>304</v>
+      </c>
+      <c r="C5" s="0">
+        <v>103</v>
+      </c>
+      <c r="D5" s="0">
+        <v>94.173169514385364</v>
+      </c>
+      <c r="E5" s="0">
+        <v>467.88</v>
+      </c>
+      <c r="F5" s="0">
+        <v>157.41555991608288</v>
+      </c>
+      <c r="G5" s="0">
+        <v>3591.2657177546312</v>
+      </c>
+      <c r="H5" s="0">
+        <v>-988.96944752242348</v>
+      </c>
+      <c r="I5" s="0">
+        <v>5.7999999999999998</v>
+      </c>
+      <c r="J5" s="0">
+        <v>14.865</v>
+      </c>
+      <c r="K5" s="0">
+        <v>2.46</v>
+      </c>
+      <c r="L5" s="0">
+        <v>3.5200000000000005</v>
+      </c>
+      <c r="M5" s="0">
+        <v>300.05811227880264</v>
+      </c>
+      <c r="N5" s="0">
+        <v>5.2729357775983692</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="0">
+        <v>103</v>
+      </c>
+      <c r="B6" s="0">
+        <v>305</v>
+      </c>
+      <c r="C6" s="0">
+        <v>103</v>
+      </c>
+      <c r="D6" s="0">
+        <v>94.153891062887084</v>
+      </c>
+      <c r="E6" s="0">
+        <v>465.69</v>
+      </c>
+      <c r="F6" s="0">
+        <v>158.15583794699666</v>
+      </c>
+      <c r="G6" s="0">
+        <v>3713.7872715984563</v>
+      </c>
+      <c r="H6" s="0">
+        <v>-1051.7511341105719</v>
+      </c>
+      <c r="I6" s="0">
+        <v>5.7999999999999998</v>
+      </c>
+      <c r="J6" s="0">
+        <v>14.43</v>
+      </c>
+      <c r="K6" s="0">
+        <v>2.4000000000000004</v>
+      </c>
+      <c r="L6" s="0">
+        <v>3.4650000000000003</v>
+      </c>
+      <c r="M6" s="0">
+        <v>300.07116527033293</v>
+      </c>
+      <c r="N6" s="0">
+        <v>5.2734613208770567</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="0">
+        <v>103</v>
+      </c>
+      <c r="B7" s="0">
+        <v>306</v>
+      </c>
+      <c r="C7" s="0">
+        <v>103</v>
+      </c>
+      <c r="D7" s="0">
+        <v>94.153891062887084</v>
+      </c>
+      <c r="E7" s="0">
+        <v>465.69</v>
+      </c>
+      <c r="F7" s="0">
+        <v>158.15583794699666</v>
+      </c>
+      <c r="G7" s="0">
+        <v>3713.7872715984563</v>
+      </c>
+      <c r="H7" s="0">
+        <v>-1051.7511341105719</v>
+      </c>
+      <c r="I7" s="0">
+        <v>5.7999999999999998</v>
+      </c>
+      <c r="J7" s="0">
+        <v>14.43</v>
+      </c>
+      <c r="K7" s="0">
+        <v>2.4000000000000004</v>
+      </c>
+      <c r="L7" s="0">
+        <v>3.4650000000000003</v>
+      </c>
+      <c r="M7" s="0">
+        <v>300.07116527033293</v>
+      </c>
+      <c r="N7" s="0">
+        <v>5.2734613208770567</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="0">
+        <v>103</v>
+      </c>
+      <c r="B8" s="0">
+        <v>307</v>
+      </c>
+      <c r="C8" s="0">
+        <v>103</v>
+      </c>
+      <c r="D8" s="0">
+        <v>94.153891062887084</v>
+      </c>
+      <c r="E8" s="0">
+        <v>465.69</v>
+      </c>
+      <c r="F8" s="0">
+        <v>158.15583794699666</v>
+      </c>
+      <c r="G8" s="0">
+        <v>3713.7872715984563</v>
+      </c>
+      <c r="H8" s="0">
+        <v>-1051.7511341105719</v>
+      </c>
+      <c r="I8" s="0">
+        <v>5.7999999999999998</v>
+      </c>
+      <c r="J8" s="0">
+        <v>14.43</v>
+      </c>
+      <c r="K8" s="0">
+        <v>2.4000000000000004</v>
+      </c>
+      <c r="L8" s="0">
+        <v>3.4650000000000003</v>
+      </c>
+      <c r="M8" s="0">
+        <v>300.07116527033293</v>
+      </c>
+      <c r="N8" s="0">
+        <v>5.2734613208770567</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="0">
+        <v>103</v>
+      </c>
+      <c r="B9" s="0">
+        <v>308</v>
+      </c>
+      <c r="C9" s="0">
+        <v>103</v>
+      </c>
+      <c r="D9" s="0">
+        <v>94.153891062887084</v>
+      </c>
+      <c r="E9" s="0">
+        <v>465.69</v>
+      </c>
+      <c r="F9" s="0">
+        <v>158.15583794699666</v>
+      </c>
+      <c r="G9" s="0">
+        <v>3713.7872715984563</v>
+      </c>
+      <c r="H9" s="0">
+        <v>-1051.7511341105719</v>
+      </c>
+      <c r="I9" s="0">
+        <v>5.7999999999999998</v>
+      </c>
+      <c r="J9" s="0">
+        <v>14.43</v>
+      </c>
+      <c r="K9" s="0">
+        <v>2.4000000000000004</v>
+      </c>
+      <c r="L9" s="0">
+        <v>3.4650000000000003</v>
+      </c>
+      <c r="M9" s="0">
+        <v>300.07116527033293</v>
+      </c>
+      <c r="N9" s="0">
+        <v>5.2734613208770567</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="0">
+        <v>103</v>
+      </c>
+      <c r="B10" s="0">
+        <v>309</v>
+      </c>
+      <c r="C10" s="0">
+        <v>103</v>
+      </c>
+      <c r="D10" s="0">
+        <v>94.153891062887084</v>
+      </c>
+      <c r="E10" s="0">
+        <v>465.69</v>
+      </c>
+      <c r="F10" s="0">
+        <v>158.15583794699666</v>
+      </c>
+      <c r="G10" s="0">
+        <v>3713.7872715984563</v>
+      </c>
+      <c r="H10" s="0">
+        <v>-1051.7511341105719</v>
+      </c>
+      <c r="I10" s="0">
+        <v>5.7999999999999998</v>
+      </c>
+      <c r="J10" s="0">
+        <v>14.43</v>
+      </c>
+      <c r="K10" s="0">
+        <v>2.4000000000000004</v>
+      </c>
+      <c r="L10" s="0">
+        <v>3.4650000000000003</v>
+      </c>
+      <c r="M10" s="0">
+        <v>300.07116527033293</v>
+      </c>
+      <c r="N10" s="0">
+        <v>5.2734613208770567</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="0">
+        <v>103</v>
+      </c>
+      <c r="B11" s="0">
+        <v>310</v>
+      </c>
+      <c r="C11" s="0">
+        <v>103</v>
+      </c>
+      <c r="D11" s="0">
+        <v>94.153891062887084</v>
+      </c>
+      <c r="E11" s="0">
+        <v>465.69</v>
+      </c>
+      <c r="F11" s="0">
+        <v>158.15583794699666</v>
+      </c>
+      <c r="G11" s="0">
+        <v>3713.7872715984563</v>
+      </c>
+      <c r="H11" s="0">
+        <v>-1051.7511341105719</v>
+      </c>
+      <c r="I11" s="0">
+        <v>5.7999999999999998</v>
+      </c>
+      <c r="J11" s="0">
+        <v>14.43</v>
+      </c>
+      <c r="K11" s="0">
+        <v>2.4000000000000004</v>
+      </c>
+      <c r="L11" s="0">
+        <v>3.4650000000000003</v>
+      </c>
+      <c r="M11" s="0">
+        <v>300.07116527033293</v>
+      </c>
+      <c r="N11" s="0">
+        <v>5.2734613208770567</v>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>